--- a/demo/registers/Workshop_Tools.xlsx
+++ b/demo/registers/Workshop_Tools.xlsx
@@ -37,123 +37,126 @@
     <t>W-100</t>
   </si>
   <si>
+    <t>Ladder 8ft</t>
+  </si>
+  <si>
+    <t>Bhavna</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>W-101</t>
+  </si>
+  <si>
+    <t>Insulation tester</t>
+  </si>
+  <si>
+    <t>Divya</t>
+  </si>
+  <si>
+    <t>W-102</t>
+  </si>
+  <si>
+    <t>Cordless drill</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>W-103</t>
+  </si>
+  <si>
     <t>Torque wrench</t>
   </si>
   <si>
+    <t>Harsh</t>
+  </si>
+  <si>
+    <t>urgent</t>
+  </si>
+  <si>
+    <t>W-104</t>
+  </si>
+  <si>
+    <t>Returned</t>
+  </si>
+  <si>
+    <t>night shift</t>
+  </si>
+  <si>
+    <t>W-105</t>
+  </si>
+  <si>
+    <t>Gauri</t>
+  </si>
+  <si>
+    <t>W-106</t>
+  </si>
+  <si>
+    <t>Crimping tool</t>
+  </si>
+  <si>
+    <t>Chirag</t>
+  </si>
+  <si>
+    <t>W-107</t>
+  </si>
+  <si>
+    <t>Multimeter</t>
+  </si>
+  <si>
+    <t>W-108</t>
+  </si>
+  <si>
+    <t>W-109</t>
+  </si>
+  <si>
+    <t>W-110</t>
+  </si>
+  <si>
+    <t>Farhan</t>
+  </si>
+  <si>
+    <t>Issued</t>
+  </si>
+  <si>
+    <t>W-111</t>
+  </si>
+  <si>
     <t>Anil</t>
   </si>
   <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>night shift</t>
-  </si>
-  <si>
-    <t>W-101</t>
-  </si>
-  <si>
-    <t>Insulation tester</t>
-  </si>
-  <si>
-    <t>Farhan</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>W-102</t>
-  </si>
-  <si>
-    <t>Chirag</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>W-103</t>
-  </si>
-  <si>
-    <t>Crimping tool</t>
-  </si>
-  <si>
-    <t>Returned</t>
-  </si>
-  <si>
-    <t>W-104</t>
-  </si>
-  <si>
-    <t>Multimeter</t>
-  </si>
-  <si>
-    <t>urgent</t>
-  </si>
-  <si>
-    <t>W-105</t>
-  </si>
-  <si>
-    <t>Cordless drill</t>
-  </si>
-  <si>
-    <t>W-106</t>
-  </si>
-  <si>
-    <t>Gauri</t>
-  </si>
-  <si>
-    <t>W-107</t>
+    <t>W-112</t>
+  </si>
+  <si>
+    <t>W-113</t>
+  </si>
+  <si>
+    <t>W-114</t>
+  </si>
+  <si>
+    <t>W-115</t>
+  </si>
+  <si>
+    <t>W-116</t>
+  </si>
+  <si>
+    <t>W-117</t>
+  </si>
+  <si>
+    <t>W-118</t>
+  </si>
+  <si>
+    <t>W-119</t>
   </si>
   <si>
     <t>Esha</t>
   </si>
   <si>
-    <t>Issued</t>
-  </si>
-  <si>
-    <t>W-108</t>
-  </si>
-  <si>
-    <t>Ladder 8ft</t>
-  </si>
-  <si>
-    <t>W-109</t>
-  </si>
-  <si>
-    <t>Bhavna</t>
-  </si>
-  <si>
-    <t>W-110</t>
-  </si>
-  <si>
-    <t>W-111</t>
-  </si>
-  <si>
-    <t>W-112</t>
-  </si>
-  <si>
-    <t>W-113</t>
-  </si>
-  <si>
-    <t>W-114</t>
-  </si>
-  <si>
-    <t>Harsh</t>
-  </si>
-  <si>
-    <t>W-115</t>
-  </si>
-  <si>
-    <t>W-116</t>
-  </si>
-  <si>
-    <t>W-117</t>
-  </si>
-  <si>
-    <t>W-118</t>
-  </si>
-  <si>
-    <t>W-119</t>
-  </si>
-  <si>
     <t>W-120</t>
   </si>
   <si>
@@ -161,9 +164,6 @@
   </si>
   <si>
     <t>W-122</t>
-  </si>
-  <si>
-    <t>Divya</t>
   </si>
   <si>
     <t>W-123</t>
@@ -629,13 +629,13 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -643,45 +643,42 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" s="2">
-        <v>46238</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -689,16 +686,19 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
+      <c r="F6" s="2">
+        <v>46239</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -709,19 +709,19 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>26</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -729,36 +729,36 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -769,7 +769,7 @@
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -781,24 +781,24 @@
         <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -806,22 +806,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -829,79 +829,82 @@
         <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>23</v>
+      </c>
+      <c r="F14" s="2">
+        <v>46247</v>
       </c>
       <c r="G14" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -909,19 +912,19 @@
         <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -929,19 +932,19 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -949,19 +952,19 @@
         <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -969,19 +972,19 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -989,33 +992,33 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -1026,22 +1029,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="2">
-        <v>46236</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -1049,22 +1049,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1072,19 +1072,19 @@
         <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>35</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1092,19 +1092,19 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1112,19 +1112,16 @@
         <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="2">
-        <v>46240</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
         <v>11</v>
@@ -1135,19 +1132,19 @@
         <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1158,10 +1155,10 @@
         <v>13</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -1175,19 +1172,19 @@
         <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1195,19 +1192,19 @@
         <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
